--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,6 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,7 +498,6 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -525,7 +524,6 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -618,17 +616,14 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -652,17 +647,14 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -686,17 +678,14 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -720,17 +709,14 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -754,17 +740,14 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -788,17 +771,14 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -822,17 +802,14 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -856,17 +833,14 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -890,17 +864,14 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -924,17 +895,14 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -958,17 +926,14 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -992,17 +957,14 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -1026,17 +988,14 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1060,17 +1019,14 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1094,17 +1050,14 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1128,17 +1081,14 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1162,17 +1112,14 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1196,17 +1143,14 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1230,7 +1174,6 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1239,8 +1182,6 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1264,7 +1205,6 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1273,8 +1213,6 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,7 +1236,6 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1307,8 +1244,6 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1332,7 +1267,6 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1341,8 +1275,6 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1366,7 +1298,6 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1375,8 +1306,6 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1400,7 +1329,6 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1409,12 +1337,284 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万元)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量24条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总出资额</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-604.5113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总出资额</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-404.5113</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总出资额</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G6" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-90.2256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总出资额</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="G7" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2318.797</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-514.2857</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,6 +471,7 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,6 +498,7 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -524,6 +525,7 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -616,14 +618,17 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -647,14 +652,17 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -678,14 +686,17 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -709,14 +720,17 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -740,14 +754,17 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -771,14 +788,17 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -802,14 +822,17 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -833,14 +856,17 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -864,14 +890,17 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -895,14 +924,17 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -926,14 +958,17 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -957,14 +992,17 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -988,14 +1026,17 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1019,14 +1060,17 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1050,14 +1094,17 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1081,14 +1128,17 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1112,14 +1162,17 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1143,14 +1196,17 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1174,6 +1230,7 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1182,6 +1239,8 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1205,6 +1264,7 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1213,6 +1273,8 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1236,6 +1298,7 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1244,6 +1307,8 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1267,6 +1332,7 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1275,6 +1341,8 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,6 +1366,7 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1306,6 +1375,8 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1329,6 +1400,7 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1337,284 +1409,12 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万元)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量24条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总出资额</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-604.5113</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总出资额</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-404.5113</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总出资额</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G6" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-90.2256</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总出资额</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="G7" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2318.797</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-514.2857</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,6 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,7 +498,6 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -525,7 +524,6 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -618,17 +616,14 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -652,17 +647,14 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -686,17 +678,14 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -720,17 +709,14 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -754,17 +740,14 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -788,17 +771,14 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -822,17 +802,14 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -856,17 +833,14 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -890,17 +864,14 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -924,17 +895,14 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -958,17 +926,14 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -992,17 +957,14 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -1026,17 +988,14 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1060,17 +1019,14 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1094,17 +1050,14 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1128,17 +1081,14 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1162,17 +1112,14 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1196,17 +1143,14 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1230,7 +1174,6 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1239,8 +1182,6 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1264,7 +1205,6 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1273,8 +1213,6 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,7 +1236,6 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1307,8 +1244,6 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1332,7 +1267,6 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1341,8 +1275,6 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1366,7 +1298,6 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1375,8 +1306,6 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1400,7 +1329,6 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1409,13 +1337,1259 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量24条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-604.5113</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H5" t="n">
+        <v>110</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>110</v>
+      </c>
+      <c r="H6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>昆山谷捷</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>780</v>
+      </c>
+      <c r="H8" t="n">
+        <v>780</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-404.5113</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>110</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>110</v>
+      </c>
+      <c r="G10" t="n">
+        <v>132</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>110</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>110</v>
+      </c>
+      <c r="G11" t="n">
+        <v>132</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>780</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>780</v>
+      </c>
+      <c r="G12" t="n">
+        <v>936</v>
+      </c>
+      <c r="H12" t="n">
+        <v>156</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-90.2256</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F14" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="G14" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>132</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>132</v>
+      </c>
+      <c r="G15" t="n">
+        <v>132</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>132</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>132</v>
+      </c>
+      <c r="G16" t="n">
+        <v>132</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F17" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="G17" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>936</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>936</v>
+      </c>
+      <c r="G18" t="n">
+        <v>936</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="E19" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2318.797</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-514.2857</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="E20" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F20" t="n">
+        <v>102.8572</v>
+      </c>
+      <c r="G20" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-51.4286</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>132</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G21" t="n">
+        <v>132</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>132</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>132</v>
+      </c>
+      <c r="G22" t="n">
+        <v>132</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="E23" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F23" t="n">
+        <v>925.7142</v>
+      </c>
+      <c r="G23" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-462.8571</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>黄山佳捷</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="G24" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>936</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>936</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="E26" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2409.0226</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3590.9774</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="E27" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F27" t="n">
+        <v>102.8572</v>
+      </c>
+      <c r="G27" t="n">
+        <v>171</v>
+      </c>
+      <c r="H27" t="n">
+        <v>68.14279999999999</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>132</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>132</v>
+      </c>
+      <c r="G28" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>132</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>132</v>
+      </c>
+      <c r="G29" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="E30" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F30" t="n">
+        <v>925.7142</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H30" t="n">
+        <v>613.2858</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>黄山佳捷</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="E31" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="F31" t="n">
+        <v>180.4512</v>
+      </c>
+      <c r="G31" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" t="n">
+        <v>119.5488</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>936</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>936</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2176.2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,6 +471,7 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,6 +498,7 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -524,6 +525,7 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -616,14 +618,17 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -647,14 +652,17 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -678,14 +686,17 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -709,14 +720,17 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -740,14 +754,17 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -771,14 +788,17 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -802,14 +822,17 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -833,14 +856,17 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -864,14 +890,17 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -895,14 +924,17 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -926,14 +958,17 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -957,14 +992,17 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -988,14 +1026,17 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1019,14 +1060,17 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1050,14 +1094,17 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1081,14 +1128,17 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1112,14 +1162,17 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1143,14 +1196,17 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1174,6 +1230,7 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1182,6 +1239,8 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1205,6 +1264,7 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1213,6 +1273,8 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1236,6 +1298,7 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1244,6 +1307,8 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1267,6 +1332,7 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1275,6 +1341,8 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,6 +1366,7 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1306,6 +1375,8 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1329,6 +1400,7 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1337,1259 +1409,13 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量24条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-604.5113</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>周斌</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>110</v>
-      </c>
-      <c r="H5" t="n">
-        <v>110</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>张俊武</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>110</v>
-      </c>
-      <c r="H6" t="n">
-        <v>110</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>昆山谷捷</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>780</v>
-      </c>
-      <c r="H8" t="n">
-        <v>780</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-404.5113</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>周斌</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>110</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>110</v>
-      </c>
-      <c r="G10" t="n">
-        <v>132</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>张俊武</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>110</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>110</v>
-      </c>
-      <c r="G11" t="n">
-        <v>132</v>
-      </c>
-      <c r="H11" t="n">
-        <v>22</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>780</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>780</v>
-      </c>
-      <c r="G12" t="n">
-        <v>936</v>
-      </c>
-      <c r="H12" t="n">
-        <v>156</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E13" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-90.2256</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上汽科技</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="F14" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="G14" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>周斌</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>132</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>132</v>
-      </c>
-      <c r="G15" t="n">
-        <v>132</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>张俊武</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>132</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>132</v>
-      </c>
-      <c r="G16" t="n">
-        <v>132</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="F17" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="G17" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>936</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>936</v>
-      </c>
-      <c r="G18" t="n">
-        <v>936</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="E19" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2318.797</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-514.2857</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上汽科技</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="E20" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="F20" t="n">
-        <v>102.8572</v>
-      </c>
-      <c r="G20" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-51.4286</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>周斌</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>132</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>132</v>
-      </c>
-      <c r="G21" t="n">
-        <v>132</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>张俊武</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>132</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>132</v>
-      </c>
-      <c r="G22" t="n">
-        <v>132</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="E23" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="F23" t="n">
-        <v>925.7142</v>
-      </c>
-      <c r="G23" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-462.8571</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>黄山佳捷</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="F24" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="G24" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>936</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>936</v>
-      </c>
-      <c r="G25" t="n">
-        <v>936</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="E26" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2409.0226</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3590.9774</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>上汽科技</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="E27" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="F27" t="n">
-        <v>102.8572</v>
-      </c>
-      <c r="G27" t="n">
-        <v>171</v>
-      </c>
-      <c r="H27" t="n">
-        <v>68.14279999999999</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>周斌</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>132</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>132</v>
-      </c>
-      <c r="G28" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>306.9</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>张俊武</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>132</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>132</v>
-      </c>
-      <c r="G29" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>306.9</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="E30" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="F30" t="n">
-        <v>925.7142</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1539</v>
-      </c>
-      <c r="H30" t="n">
-        <v>613.2858</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>黄山佳捷</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="F31" t="n">
-        <v>180.4512</v>
-      </c>
-      <c r="G31" t="n">
-        <v>300</v>
-      </c>
-      <c r="H31" t="n">
-        <v>119.5488</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>936</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>936</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3112.2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2176.2</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,6 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,7 +498,6 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -525,7 +524,6 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -618,17 +616,14 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -652,17 +647,14 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -686,17 +678,14 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -720,17 +709,14 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -754,17 +740,14 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -788,17 +771,14 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -822,17 +802,14 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -856,17 +833,14 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -890,17 +864,14 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -924,17 +895,14 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -958,17 +926,14 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -992,17 +957,14 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -1026,17 +988,14 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1060,17 +1019,14 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1094,17 +1050,14 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1128,17 +1081,14 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1162,17 +1112,14 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1196,17 +1143,14 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1230,7 +1174,6 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1239,8 +1182,6 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1264,7 +1205,6 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1273,8 +1213,6 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,7 +1236,6 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1307,8 +1244,6 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1332,7 +1267,6 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1341,8 +1275,6 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1366,7 +1298,6 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1375,8 +1306,6 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1400,7 +1329,6 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1409,12 +1337,322 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量24条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-604.5113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-404.5113</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G6" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-90.2256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1714.2857</v>
+      </c>
+      <c r="G7" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2318.797</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-514.2857</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1804.5113</v>
+      </c>
+      <c r="G8" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2409.0226</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3590.9774</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,6 +471,7 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,6 +498,7 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -524,6 +525,7 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -616,14 +618,17 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -647,14 +652,17 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -678,14 +686,17 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -709,14 +720,17 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -740,14 +754,17 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -771,14 +788,17 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -802,14 +822,17 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -833,14 +856,17 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -864,14 +890,17 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -895,14 +924,17 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -926,14 +958,17 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -957,14 +992,17 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -988,14 +1026,17 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1019,14 +1060,17 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1050,14 +1094,17 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1081,14 +1128,17 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1112,14 +1162,17 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1143,14 +1196,17 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1174,6 +1230,7 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1182,6 +1239,8 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1205,6 +1264,7 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1213,6 +1273,8 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1236,6 +1298,7 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1244,6 +1307,8 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1267,6 +1332,7 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1275,6 +1341,8 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,6 +1366,7 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1306,6 +1375,8 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1329,6 +1400,7 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1337,322 +1409,12 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量24条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-604.5113</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1604.5113</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-404.5113</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G6" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-90.2256</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1714.2857</v>
-      </c>
-      <c r="G7" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2318.797</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-514.2857</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>1804.5113</v>
-      </c>
-      <c r="G8" t="n">
-        <v>604.5113</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2409.0226</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3590.9774</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,9 @@
       <c r="D2" t="n">
         <v>462.8571</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>462.8571</v>
+      </c>
       <c r="F2" t="n">
         <v>22.42</v>
       </c>
@@ -498,7 +501,9 @@
       <c r="D3" t="n">
         <v>51.4286</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>51.4286</v>
+      </c>
       <c r="F3" t="n">
         <v>22.42</v>
       </c>
@@ -525,7 +530,9 @@
       <c r="D4" t="n">
         <v>90.2256</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>90.2256</v>
+      </c>
       <c r="F4" t="n">
         <v>23.55</v>
       </c>
@@ -618,17 +625,14 @@
       <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>昆山谷捷</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
@@ -652,17 +656,14 @@
       <c r="D3" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>780</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -686,17 +687,14 @@
       <c r="D4" t="n">
         <v>1000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>110</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -720,17 +718,14 @@
       <c r="D5" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>110</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
@@ -754,17 +749,14 @@
       <c r="D6" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>936</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -788,17 +780,14 @@
       <c r="D7" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>132</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -822,17 +811,14 @@
       <c r="D8" t="n">
         <v>1200</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>132</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
@@ -856,17 +842,14 @@
       <c r="D9" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>936</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -890,17 +873,14 @@
       <c r="D10" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>132</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -924,17 +904,14 @@
       <c r="D11" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>132</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -958,17 +935,14 @@
       <c r="D12" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -992,17 +966,14 @@
       <c r="D13" t="n">
         <v>1714.2857</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
@@ -1026,17 +997,14 @@
       <c r="D14" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>936</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1060,17 +1028,14 @@
       <c r="D15" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1094,17 +1059,14 @@
       <c r="D16" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1128,17 +1090,14 @@
       <c r="D17" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>赛格高技术</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>462.8571</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1162,17 +1121,14 @@
       <c r="D18" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>51.4286</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1196,17 +1152,14 @@
       <c r="D19" t="n">
         <v>1804.5113</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>90.2256</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
@@ -1230,7 +1183,6 @@
       <c r="D20" t="n">
         <v>6000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
@@ -1239,8 +1191,6 @@
       <c r="G20" t="n">
         <v>3112.2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1264,7 +1214,6 @@
       <c r="D21" t="n">
         <v>6000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
@@ -1273,8 +1222,6 @@
       <c r="G21" t="n">
         <v>438.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1298,7 +1245,6 @@
       <c r="D22" t="n">
         <v>6000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
@@ -1307,8 +1253,6 @@
       <c r="G22" t="n">
         <v>438.9</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1332,7 +1276,6 @@
       <c r="D23" t="n">
         <v>6000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>赛格高技术</t>
@@ -1341,8 +1284,6 @@
       <c r="G23" t="n">
         <v>1539</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1366,7 +1307,6 @@
       <c r="D24" t="n">
         <v>6000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
@@ -1375,8 +1315,6 @@
       <c r="G24" t="n">
         <v>171</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
@@ -1400,7 +1338,6 @@
       <c r="D25" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>黄山佳捷</t>
@@ -1409,11 +1346,119 @@
       <c r="G25" t="n">
         <v>300</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量24条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让3条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -1363,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,20 +1374,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1402,17 +1427,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3条,字段完整</t>
         </is>
       </c>
     </row>
@@ -1425,40 +1455,1292 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量24条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让3条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1604.5113</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3990</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2385.4887</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E5" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4594.5113</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3990</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-604.5113</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E6" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4594.5113</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5700</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1105.4887</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5700</v>
+      </c>
+      <c r="E7" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6304.5113</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-304.5113</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>604.5113</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6604.5113</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-604.5113</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>昆山谷捷</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F16" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="G16" t="n">
+        <v>171</v>
+      </c>
+      <c r="H16" t="n">
+        <v>119.5714</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F19" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1076.1429</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>171</v>
+      </c>
+      <c r="E21" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F21" t="n">
+        <v>222.4286</v>
+      </c>
+      <c r="G21" t="n">
+        <v>171</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-51.4286</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1539</v>
+      </c>
+      <c r="E24" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2001.8571</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-462.8571</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>黄山佳捷</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="F25" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="G25" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" t="n">
+        <v>209.7744</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>171</v>
+      </c>
+      <c r="E27" t="n">
+        <v>51.4286</v>
+      </c>
+      <c r="F27" t="n">
+        <v>222.4286</v>
+      </c>
+      <c r="G27" t="n">
+        <v>171</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-51.4286</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1539</v>
+      </c>
+      <c r="E30" t="n">
+        <v>462.8571</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2001.8571</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-462.8571</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>黄山佳捷</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>300</v>
+      </c>
+      <c r="E31" t="n">
+        <v>90.2256</v>
+      </c>
+      <c r="F31" t="n">
+        <v>390.2256</v>
+      </c>
+      <c r="G31" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-90.2256</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1股东</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>t0比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>t1比例合计66.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>t2比例合计66.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5股东</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>t3比例合计95.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6股东</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>t4比例合计100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6股东</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>t5比例合计100.00%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,95 +609,87 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>报告期初公司股权结构（有限公司设立时）</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1000</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>昆山谷捷</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>51.87</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2012年6月12日，谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2021年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1000</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>黄山供销集团</t>
+          <t>赛格高技术</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3112.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>780</v>
-      </c>
+        <v>1539</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>51.87</v>
+        <v>25.65</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2021年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1000</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
@@ -707,35 +699,31 @@
       <c r="G4" t="n">
         <v>438.9</v>
       </c>
-      <c r="H4" t="n">
-        <v>110</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7.315</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2021年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1000</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
@@ -745,728 +733,644 @@
       <c r="G5" t="n">
         <v>438.9</v>
       </c>
-      <c r="H5" t="n">
-        <v>110</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7.315</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本次股权转让后，谷捷有限的股权结构如下：黄山供销集团出资780万元，占比78%；张俊武出资110万元，占比11%；周斌出资110万元，占比11%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2021年4月吸收合并后股权结构</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1200</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>黄山供销集团</t>
+          <t>黄山佳捷</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3112.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>936</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>51.87</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2021年4月吸收合并后股权结构</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1200</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上汽科技</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>132</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>7.315</v>
+        <v>2.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2021年4月吸收合并后股权结构</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1200</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>6,000.00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>132</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7.315</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2021年4月7日，谷捷有限召开股东会，吸收合并后谷捷有限的注册资本变更为1,200万元，其中黄山供销集团出资936万元，张俊武出资132万元，周斌出资132万元。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2021年11月第一次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1714.2857</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>黄山供销集团</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>3112.2</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>936</v>
+        <v>780</v>
       </c>
       <c r="I9" t="n">
-        <v>51.87</v>
+        <v>78</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021年11月第一次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1714.2857</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="I10" t="n">
-        <v>7.315</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2021年11月第一次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1714.2857</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="I11" t="n">
-        <v>7.315</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>本次发行后 | 股份公司设立</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2021年11月第一次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1714.2857</v>
-      </c>
+          <t>本次发行后 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1539</v>
-      </c>
+          <t>1,000.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>462.8571</v>
-      </c>
-      <c r="I12" t="n">
-        <v>25.65</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
+          <t>Markdown表格: 本次发行后 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2021年11月第一次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1714.2857</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上汽科技</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>171</v>
-      </c>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>51.4286</v>
+        <v>936</v>
       </c>
       <c r="I13" t="n">
-        <v>2.85</v>
+        <v>54.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>本次增资完成后，公司股权结构如下：黄山供销集团出资936万元，占比54.6%；张俊武出资132万元，占比7.7%；周斌出资132万元，占比7.7%；赛格高技术出资462.8571万元，占比27.0%；上汽科技出资51.4286万元，占比3.0%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>3112.2</v>
-      </c>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>936</v>
+        <v>462.8571</v>
       </c>
       <c r="I14" t="n">
-        <v>51.87</v>
+        <v>27</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>132</v>
       </c>
       <c r="I15" t="n">
-        <v>7.315</v>
+        <v>7.7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>132</v>
       </c>
       <c r="I16" t="n">
-        <v>7.315</v>
+        <v>7.7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1539</v>
-      </c>
+          <t>上汽科技</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>462.8571</v>
+        <v>51.4286</v>
       </c>
       <c r="I17" t="n">
-        <v>25.65</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>上汽科技</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>171</v>
-      </c>
+          <t>1,714.2857</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>51.4286</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.85</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 4、2021 年 11 月，第一次增资，增资至 1,714.2857 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022年5月第二次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1804.5113</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>黄山佳捷</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>300</v>
-      </c>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>90.2256</v>
+        <v>936</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>51.87</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>本次增资完成后，谷捷有限的股权结构如下：黄山供销集团出资936万元，占比51.87%；张俊武出资132万元，占比7.32%；周斌出资132万元，占比7.32%；赛格高技术出资462.8571万元，占比25.65%；上汽科技出资51.4286万元，占比2.85%；黄山佳捷出资90.2256万元，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>黄山供销集团</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>3112.2</v>
-      </c>
+          <t>赛格高技术</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>780</v>
+        <v>462.8571</v>
       </c>
       <c r="I20" t="n">
-        <v>51.87</v>
+        <v>25.65</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>张俊武</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I21" t="n">
         <v>7.315</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>周斌</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>438.9</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I22" t="n">
         <v>7.315</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>赛格高技术</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1539</v>
-      </c>
+          <t>黄山佳捷</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>462.8571</v>
+        <v>90.2256</v>
       </c>
       <c r="I23" t="n">
-        <v>25.65</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>上汽科技</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>171</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>51.4286</v>
       </c>
@@ -1475,45 +1379,243 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2022年9月整体变更为股份公司后股权结构</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>6000</v>
-      </c>
+          <t>5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
+          <t>1,804.5113</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Markdown表格: 5、2022 年 5 月，第二次增资，增资至 1,804.5113 万元 | 增资完成后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>黄山供销集团</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3112.2</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>赛格高技术(CS)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>张俊武</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>7.315</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>周斌</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>7.315</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>黄山佳捷</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G30" t="n">
         <v>300</v>
       </c>
-      <c r="H25" t="n">
-        <v>90.2256</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>本次整体变更后，黄山谷捷的股权结构如下：黄山供销集团持股3112.20万股，占比51.87%；张俊武持股438.90万股，占比7.315%；周斌持股438.90万股，占比7.315%；赛格高技术持股1539.00万股，占比25.65%；上汽科技持股171.00万股，占比2.85%；黄山佳捷持股300.00万股，占比5.00%。</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>（二）本次发行前的前十名股东情况 | 本次发行后</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>上汽科技(CS)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>171</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Markdown表格: （二）本次发行前的前十名股东情况 | 本次发行后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
